--- a/currentbuild/CodeSystem-person-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-person-public-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:03:39+00:00</t>
+    <t>2026-04-16T08:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
